--- a/fixtures/legacy/old-app-export.xlsx
+++ b/fixtures/legacy/old-app-export.xlsx
@@ -144,10 +144,10 @@
     <t>Mathematics and Statistics</t>
   </si>
   <si>
-    <t>MATH</t>
-  </si>
-  <si>
-    <t>101</t>
+    <t>MUSC</t>
+  </si>
+  <si>
+    <t>104</t>
   </si>
   <si>
     <t>A</t>
@@ -165,7 +165,7 @@
     <t>NH 101</t>
   </si>
   <si>
-    <t>Calculus I</t>
+    <t>Musical Patterns I</t>
   </si>
   <si>
     <t>Lecture</t>
@@ -177,7 +177,7 @@
     <t>In-Person</t>
   </si>
   <si>
-    <t>102</t>
+    <t>105</t>
   </si>
   <si>
     <t>11:00:00</t>
@@ -186,10 +186,10 @@
     <t>NH 102</t>
   </si>
   <si>
-    <t>Calculus II</t>
-  </si>
-  <si>
-    <t>231</t>
+    <t>Musical Patterns II</t>
+  </si>
+  <si>
+    <t>234</t>
   </si>
   <si>
     <t>TR</t>
@@ -201,16 +201,16 @@
     <t>NH 103</t>
   </si>
   <si>
-    <t>Linear Algebra</t>
+    <t>Harmonic Structures</t>
   </si>
   <si>
     <t>200</t>
   </si>
   <si>
-    <t>STAT</t>
-  </si>
-  <si>
-    <t>143</t>
+    <t>URBS</t>
+  </si>
+  <si>
+    <t>146</t>
   </si>
   <si>
     <t>12:15:00</t>
@@ -219,19 +219,19 @@
     <t>NH 105</t>
   </si>
   <si>
-    <t>Introduction to Statistics</t>
-  </si>
-  <si>
-    <t>243</t>
-  </si>
-  <si>
-    <t>Statistical Methods</t>
-  </si>
-  <si>
-    <t>DATA</t>
-  </si>
-  <si>
-    <t>202</t>
+    <t>Introduction to Behavioral Dynamics</t>
+  </si>
+  <si>
+    <t>246</t>
+  </si>
+  <si>
+    <t>Behavioral Methods</t>
+  </si>
+  <si>
+    <t>DIGI</t>
+  </si>
+  <si>
+    <t>205</t>
   </si>
   <si>
     <t>Fay Mockson</t>
@@ -243,16 +243,16 @@
     <t>SB 110</t>
   </si>
   <si>
-    <t>Data Computing</t>
+    <t>Information Computing</t>
   </si>
   <si>
     <t>Hybrid</t>
   </si>
   <si>
-    <t>CS</t>
-  </si>
-  <si>
-    <t>108</t>
+    <t>CRUD</t>
+  </si>
+  <si>
+    <t>111</t>
   </si>
   <si>
     <t>Gus Testwell</t>
@@ -261,7 +261,7 @@
     <t>SB 120</t>
   </si>
   <si>
-    <t>Introduction to Computing</t>
+    <t>Introduction to Urban Systems</t>
   </si>
   <si>
     <t>HNRS</t>
@@ -294,13 +294,13 @@
     <t>The registrar assigns the letter</t>
   </si>
   <si>
-    <t>232</t>
-  </si>
-  <si>
-    <t>Multivariable Calculus</t>
-  </si>
-  <si>
-    <t>302</t>
+    <t>235</t>
+  </si>
+  <si>
+    <t>Multivoice Analysis</t>
+  </si>
+  <si>
+    <t>305</t>
   </si>
   <si>
     <t>14:10:00</t>
@@ -309,13 +309,13 @@
     <t>NH 104</t>
   </si>
   <si>
-    <t>Real Analysis II</t>
+    <t>Corpus Studies II</t>
   </si>
   <si>
     <t>300</t>
   </si>
   <si>
-    <t>391</t>
+    <t>394</t>
   </si>
   <si>
     <t xml:space="preserve">R
@@ -336,13 +336,13 @@
     <t>Colloquium</t>
   </si>
   <si>
-    <t>244</t>
-  </si>
-  <si>
-    <t>Regression Models</t>
-  </si>
-  <si>
-    <t>301</t>
+    <t>247</t>
+  </si>
+  <si>
+    <t>Models of Change</t>
+  </si>
+  <si>
+    <t>304</t>
   </si>
   <si>
     <t>Fay Mockson, Ben Sample</t>
@@ -351,13 +351,13 @@
     <t>MW</t>
   </si>
   <si>
-    <t>Data Science Topics</t>
+    <t>Digital Information Topics</t>
   </si>
   <si>
     <t>Online (synchronous)</t>
   </si>
   <si>
-    <t>262</t>
+    <t>265</t>
   </si>
   <si>
     <t>Hal Fakename</t>
@@ -369,7 +369,7 @@
     <t>SB 122</t>
   </si>
   <si>
-    <t>Data Structures</t>
+    <t>Urban Data Structures</t>
   </si>
   <si>
     <t>StudentCredits</t>
